--- a/docs/requirements-tracking/需求完成度跟踪表.xlsx
+++ b/docs/requirements-tracking/需求完成度跟踪表.xlsx
@@ -578,8 +578,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CompletedItems" displayName="CompletedItems" ref="A33:C42" headerRowCount="1">
-  <autoFilter ref="A33:C42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="CompletedItems" displayName="CompletedItems" ref="A33:C43" headerRowCount="1">
+  <autoFilter ref="A33:C43"/>
   <tableColumns count="3">
     <tableColumn id="1" name="日期"/>
     <tableColumn id="2" name="完成项"/>
@@ -590,8 +590,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PendingConfirmations" displayName="PendingConfirmations" ref="A46:C53" headerRowCount="1">
-  <autoFilter ref="A46:C53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PendingConfirmations" displayName="PendingConfirmations" ref="A47:C54" headerRowCount="1">
+  <autoFilter ref="A47:C54"/>
   <tableColumns count="3">
     <tableColumn id="1" name="编号"/>
     <tableColumn id="2" name="待确认问题"/>
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>请求/评论/附件按角色和组织校验，动作写入 history</t>
+          <t>请求/评论/附件按角色校验，动作写入 history；组织 scope 已废除</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>组织、用户、角色、权限、团队、路由、审计和 Dashboard</t>
+          <t>用户、角色、权限、团队、路由、审计和 Dashboard</t>
         </is>
       </c>
       <c r="D38" s="2" t="n"/>
@@ -1856,9 +1856,21 @@
       <c r="I42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>废除组织管理</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>移除 Organization 页面、主流程字段、前端 API/types；V1.0.29 放开 team.org_id</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
@@ -1878,11 +1890,7 @@
       <c r="I44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>待确认项</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n"/>
@@ -1893,21 +1901,13 @@
       <c r="I45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>待确认问题</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>当前实现 / 建议</t>
-        </is>
-      </c>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>待确认项</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
@@ -1916,19 +1916,19 @@
       <c r="I46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>CONF-001</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>普通用户查看他人请求的详情字段和公开留言范围</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>当前按组织范围控制访问，上线前确认字段粒度</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>待确认问题</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>当前实现 / 建议</t>
         </is>
       </c>
       <c r="D47" s="2" t="n"/>
@@ -1941,17 +1941,17 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>CONF-002</t>
+          <t>CONF-001</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Team Queue 是全 IT 还是仅团队可见</t>
+          <t>普通用户查看他人请求的详情字段和公开留言范围</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>当前 IT 范围较开放，上线前确认 scope</t>
+          <t>组织范围已废除，上线前确认字段粒度</t>
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
@@ -1964,17 +1964,17 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>CONF-003</t>
+          <t>CONF-002</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Team Lead 是否可负责多个团队</t>
+          <t>Team Queue 是全 IT 还是仅团队可见</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>模型保留扩展空间，业务规则待定</t>
+          <t>当前 IT 范围较开放，上线前确认 scope</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -1987,17 +1987,17 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>CONF-004</t>
+          <t>CONF-003</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Closed 是否允许重新打开</t>
+          <t>Team Lead 是否可负责多个团队</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>当前为终态，建议 P2</t>
+          <t>模型保留扩展空间，业务规则待定</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -2010,17 +2010,17 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>CONF-005</t>
+          <t>CONF-004</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>用户是否需要物理删除</t>
+          <t>Closed 是否允许重新打开</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>当前启用/禁用，建议禁用优先</t>
+          <t>当前为终态，建议 P2</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
@@ -2033,17 +2033,17 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>CONF-006</t>
+          <t>CONF-005</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Audit Logs 是否需要导出</t>
+          <t>用户是否需要物理删除</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>建议 P1</t>
+          <t>当前启用/禁用，建议禁用优先</t>
         </is>
       </c>
       <c r="D52" s="2" t="n"/>
@@ -2056,17 +2056,17 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>CONF-007</t>
+          <t>CONF-006</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Docker 运行验证</t>
+          <t>Audit Logs 是否需要导出</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>启动 Docker Desktop 后重建并执行多角色端到端验证</t>
+          <t>建议 P1</t>
         </is>
       </c>
       <c r="D53" s="2" t="n"/>
@@ -2076,13 +2076,36 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>CONF-007</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Docker 运行验证</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>启动 Docker Desktop 后重建并执行多角色端到端验证</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A46:I46"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A45:I45"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -2141,7 +2164,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Admin 管理组织、账号、权限、团队、路由、全局请求和审计，也可作为全局技术负责人。</t>
+          <t>Admin 管理账号、权限、团队、路由、全局请求和审计，也可作为全局技术负责人。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2242,7 +2265,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>组织/用户/角色/权限</t>
+          <t>用户/角色/权限</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2251,11 +2274,11 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>页面和 system API 使用真实 CRUD</t>
+          <t>页面和 system API 使用真实 CRUD；用户不再绑定组织</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2280,16 +2303,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>真实成员、负责人、路由规则和自动匹配</t>
+          <t>真实成员、负责人、路由规则和自动匹配；团队不再绑定组织</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>V1.0.25 实库验证</t>
+          <t>V1.0.29 实库验证</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
@@ -2459,7 +2482,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>管理组织</t>
+          <t>废除组织管理</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2467,27 +2490,27 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>进行中</t>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>OrganizationList.vue + Organization CRUD API</t>
+          <t>删除 Organization 页面、路由、前端 API/types；主流程不再出现 organization</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Docker 待验证</t>
+          <t>旧隐藏 CMDB 文件保留历史字段</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>组织层级深度</t>
+          <t>已确认以团队为主</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr"/>
@@ -2514,11 +2537,11 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>UserList.vue + User CRUD API</t>
+          <t>UserList.vue + User CRUD API；不再分配组织</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -2596,11 +2619,11 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>TeamList.vue、V1.0.25、Team/User DTO</t>
+          <t>TeamList.vue、V1.0.25、V1.0.29、Team/User DTO</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -2914,7 +2937,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Organizations / Users</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -3411,11 +3434,11 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>真实 create API、富文本、时间字段、粘贴图片和附件</t>
+          <t>真实 create API、富文本、时间字段、粘贴图片和附件；不再选择组织</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3538,11 +3561,11 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>后端组织范围访问控制</t>
+          <t>组织 scope 已废除，请求读取不再按 organization 限制</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
@@ -4463,7 +4486,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Assignee 显示 team/org + assign API</t>
+          <t>Assignee 显示 team + assign API</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -6056,7 +6079,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>真实 assign API，人员显示 team/org</t>
+          <t>真实 assign API，人员显示 team</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
